--- a/ejemplos/excel_prueba.xlsx
+++ b/ejemplos/excel_prueba.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,7 +564,6 @@
           <t>RURAL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>APARTADO</t>
@@ -575,13 +574,11 @@
           <t>CHIGORODO</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>FINCA BUENA VISTA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>008-2077</t>
@@ -627,7 +624,6 @@
           <t>FINCA BUENA VISTA</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>NOROCCIDENTE</t>
@@ -675,7 +671,6 @@
           <t>URBANO</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>MEDELLIN SUR</t>
@@ -686,13 +681,11 @@
           <t>MEDELLIN</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>CL 10 # 40-20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>1555</t>
@@ -728,15 +721,11 @@
           <t>MEDELLIN</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CALLE 10 40 20</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>NO</t>
@@ -789,13 +778,11 @@
           <t>BOGOTA</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>KR 7 32 16</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>50C-77777</t>
@@ -831,13 +818,11 @@
           <t>BOGOTA D.C.</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>KR 7 32 16</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>CENTRAL</t>
@@ -861,6 +846,216 @@
       <c r="Y4" t="inlineStr">
         <is>
           <t>A-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>040-30938</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CARRETERA A LA PLAYA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>040-30938</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>M-4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>LOTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ATLANTICO</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CARRETERA A LA PLAYA</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VICTOR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>041-5555</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SABANALARGA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BARANOA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>VILLA JOSE LO 5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>041-5555</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>M-5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>LOTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ATLANTICO</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>BARANOA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>VILLA JOSE LO 5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>08078000100000063000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>A-5</t>
         </is>
       </c>
     </row>
